--- a/frontend/dashboard/output/generated_timetable.xlsx
+++ b/frontend/dashboard/output/generated_timetable.xlsx
@@ -495,37 +495,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Discrete Mathematics (Sri. P Gopala Krishna)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Digital Logic Design (Dr. Y J Nagendra Kumar)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Break</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Discrete Mathematics (Sri. P Gopala Krishna)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Database Management Systems Lab (Dr. V N Ganapathi Raju)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>Java Programming (Dr. K. Prasanna Lakshmi)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Discrete Mathematics (Dr. Y Srilalitha)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Break</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Database Management Systems Lab (Ms. I Laxmi Bindu)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Probability and Statistics (Dr. K. Prasanna Lakshmi)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Digital Logic Design (Dr. Y J Nagendra Kumar)</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Discrete Mathematics (Dr. Y Srilalitha)</t>
+          <t>Database Management Systems (Dr. Y Srilalitha)</t>
         </is>
       </c>
     </row>
@@ -537,12 +537,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Discrete Mathematics (Dr. Y Srilalitha)</t>
+          <t>Java Programming Lab (Mrs. N Mounika)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Probability and Statistics (Dr. K. Prasanna Lakshmi)</t>
+          <t>Digital Electronics Lab (Mr. P K Abhilash)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -557,17 +557,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Digital Electronics Lab (Mr. P K Abhilash)</t>
+          <t>Probability and Statistics (Mrs. P Prathibha Swaraj)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Digital Logic Design (Dr. Y J Nagendra Kumar)</t>
+          <t>Java Programming (Dr. K. Prasanna Lakshmi)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Java Programming (Dr. K. Prasanna Lakshmi)</t>
+          <t>Discrete Mathematics (Sri. P Gopala Krishna)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -589,12 +589,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Discrete Mathematics (Dr. Y Srilalitha)</t>
+          <t>Java Programming Lab (Mrs. N Mounika)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Probability and Statistics (Dr. K. Prasanna Lakshmi)</t>
+          <t>Database Management Systems Lab (Dr. V N Ganapathi Raju)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -604,22 +604,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Database Management Systems (Dr. Y Srilalitha)</t>
+          <t>Java Programming (Dr. K. Prasanna Lakshmi)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Database Management Systems (Dr. Y Srilalitha)</t>
+          <t>Probability and Statistics (Mrs. P Prathibha Swaraj)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Java Programming Lab (Mrs. N Mounika)</t>
+          <t>Probability and Statistics (Mrs. P Prathibha Swaraj)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Discrete Mathematics (Dr. Y Srilalitha)</t>
+          <t>Digital Logic Design (Dr. Y J Nagendra Kumar)</t>
         </is>
       </c>
     </row>
@@ -631,17 +631,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Database Management Systems Lab (Ms. I Laxmi Bindu)</t>
+          <t>Digital Logic Design (Dr. Y J Nagendra Kumar)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Database Management Systems Lab (Ms. I Laxmi Bindu)</t>
+          <t>Discrete Mathematics (Sri. P Gopala Krishna)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Digital Logic Design (Dr. Y J Nagendra Kumar)</t>
+          <t>Probability and Statistics (Mrs. P Prathibha Swaraj)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Database Management Systems (Dr. Y Srilalitha)</t>
+          <t>Digital Electronics Lab (Mr. P K Abhilash)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Probability and Statistics (Dr. K. Prasanna Lakshmi)</t>
+          <t>Java Programming (Dr. K. Prasanna Lakshmi)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -678,17 +678,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Java Programming (Dr. K. Prasanna Lakshmi)</t>
+          <t>Discrete Mathematics (Sri. P Gopala Krishna)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Probability and Statistics (Dr. K. Prasanna Lakshmi)</t>
+          <t>Database Management Systems Lab (Dr. V N Ganapathi Raju)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Java Programming Lab (Mrs. N Mounika)</t>
+          <t>Probability and Statistics (Mrs. P Prathibha Swaraj)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Digital Electronics Lab (Mr. P K Abhilash)</t>
+          <t>Database Management Systems (Dr. Y Srilalitha)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Java Programming (Dr. K. Prasanna Lakshmi)</t>
+          <t>Digital Logic Design (Dr. Y J Nagendra Kumar)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Digital Logic Design (Dr. Y J Nagendra Kumar)</t>
+          <t>Database Management Systems (Dr. Y Srilalitha)</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Value Ethics and Gender Culture (Mrs. N Mounika)</t>
+          <t>Java Programming Lab (Ms. I Laxmi Bindu)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Value Ethics and Gender Culture (Dr. V Akila)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>Digital Electronics Lab (Mrs.L.Hema Lalitha)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Digital Logic Design (Dr. Y J Nagendra Kumar)</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Break</t>
@@ -814,22 +814,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Discrete Mathematics (Sri. P Gopala Krishna)</t>
+          <t>Probability and Statistics (Mrs. P Prathibha Swaraj)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Database Management Systems Lab (Dr. V N Ganapathi Raju)</t>
+          <t>Discrete Mathematics (Dr. Y Srilalitha)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Java Programming (Dr. K. Prasanna Lakshmi)</t>
+          <t>Java Programming Lab (Ms. I Laxmi Bindu)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Discrete Mathematics (Sri. P Gopala Krishna)</t>
+          <t>Digital Electronics Lab (Mrs.L.Hema Lalitha)</t>
         </is>
       </c>
     </row>
@@ -841,42 +841,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Digital Electronics Lab (Mrs.L.Hema Lalitha)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Discrete Mathematics (Dr. Y Srilalitha)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Digital Logic Design (Dr. Y J Nagendra Kumar)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Break</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Database Management Systems (Mrs. T. Nishitha)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>Java Programming Lab (Ms. I Laxmi Bindu)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Digital Logic Design (Dr. Y J Nagendra Kumar)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Java Programming (Dr. K. Prasanna Lakshmi)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Probability and Statistics (Mrs. P Prathibha Swaraj)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Break</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Database Management Systems (Dr. V N Ganapathi Raju)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Java Programming (Dr. K. Prasanna Lakshmi)</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Discrete Mathematics (Sri. P Gopala Krishna)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Java Programming Lab (Ms. I Laxmi Bindu)</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Database Management Systems Lab (Dr. V N Ganapathi Raju)</t>
+          <t>Database Management Systems (Mrs. T. Nishitha)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -898,32 +898,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Database Management Systems Lab (Mrs. M Kanaka Durga Bella)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Break</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Digital Logic Design (Dr. Y J Nagendra Kumar)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Break</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Digital Electronics Lab (Mrs.L.Hema Lalitha)</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Database Management Systems (Dr. V N Ganapathi Raju)</t>
+          <t>Digital Logic Design (Dr. Y J Nagendra Kumar)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Java Programming (Dr. K. Prasanna Lakshmi)</t>
+          <t>Database Management Systems (Mrs. T. Nishitha)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Database Management Systems (Dr. V N Ganapathi Raju)</t>
+          <t>Probability and Statistics (Mrs. P Prathibha Swaraj)</t>
         </is>
       </c>
     </row>
@@ -935,42 +935,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Discrete Mathematics (Dr. Y Srilalitha)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Java Programming (Dr. K. Prasanna Lakshmi)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Database Management Systems Lab (Mrs. M Kanaka Durga Bella)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Break</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Digital Logic Design (Dr. Y J Nagendra Kumar)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>Probability and Statistics (Mrs. P Prathibha Swaraj)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Database Management Systems Lab (Dr. V N Ganapathi Raju)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Database Management Systems (Dr. V N Ganapathi Raju)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Break</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Digital Electronics Lab (Mrs.L.Hema Lalitha)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Digital Logic Design (Dr. Y J Nagendra Kumar)</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Probability and Statistics (Mrs. P Prathibha Swaraj)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Java Programming Lab (Ms. I Laxmi Bindu)</t>
         </is>
       </c>
     </row>
@@ -982,17 +982,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Probability and Statistics (Mrs. P Prathibha Swaraj)</t>
+          <t>Database Management Systems Lab (Mrs. M Kanaka Durga Bella)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Digital Logic Design (Dr. Y J Nagendra Kumar)</t>
+          <t>Java Programming (Dr. K. Prasanna Lakshmi)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Database Management Systems (Dr. V N Ganapathi Raju)</t>
+          <t>Database Management Systems (Mrs. T. Nishitha)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Probability and Statistics (Mrs. P Prathibha Swaraj)</t>
+          <t>Discrete Mathematics (Dr. Y Srilalitha)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Discrete Mathematics (Sri. P Gopala Krishna)</t>
+          <t>Discrete Mathematics (Dr. Y Srilalitha)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Discrete Mathematics (Sri. P Gopala Krishna)</t>
+          <t>Database Management Systems (Mrs. T. Nishitha)</t>
         </is>
       </c>
     </row>
@@ -1098,42 +1098,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Digital Electronics Lab (Mrs.L.Hema Lalitha)</t>
+          <t>Java Programming (Dr. Y J Nagendra Kumar)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Probability and Statistics (Dr. K. Prasanna Lakshmi)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Probability and Statistics (Dr. K. Prasanna Lakshmi)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Break</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Digital Logic Design (Mrs. Y Prasanna)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Digital Electronics Lab (Mrs.L.Hema Lalitha)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Break</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Java Programming (Dr. Y J Nagendra Kumar)</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Discrete Mathematics (Dr. Y Srilalitha)</t>
+          <t>Java Programming Lab (Mrs. A Srilakshmi)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Discrete Mathematics (Dr. Y Srilalitha)</t>
+          <t>Digital Logic Design (Mrs. Y Prasanna)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Java Programming (Dr. Y J Nagendra Kumar)</t>
+          <t>Digital Electronics Lab (Mr. P K Abhilash)</t>
         </is>
       </c>
     </row>
@@ -1145,42 +1145,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Digital Logic Design (Mrs. Y Prasanna)</t>
+          <t>Database Management Systems (Dr. V N Ganapathi Raju)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Discrete Mathematics (Dr. Y Srilalitha)</t>
+          <t>Probability and Statistics (Dr. K. Prasanna Lakshmi)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Database Management Systems Lab (Ms. I Laxmi Bindu)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Break</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Database Management Systems Lab (Ms. I Laxmi Bindu)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Discrete Mathematics (Sri. P Gopala Krishna)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Database Management Systems (Dr. V N Ganapathi Raju)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>Java Programming (Dr. Y J Nagendra Kumar)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Break</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Probability and Statistics (Dr. K. Prasanna Lakshmi)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Java Programming Lab (Mrs. A Srilakshmi)</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Java Programming Lab (Mrs. A Srilakshmi)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Database Management Systems (Mrs. T. Nishitha)</t>
         </is>
       </c>
     </row>
@@ -1192,19 +1192,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Probability and Statistics (Dr. K. Prasanna Lakshmi)</t>
+          <t>Java Programming Lab (Mrs. A Srilakshmi)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Database Management Systems (Dr. V N Ganapathi Raju)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Digital Logic Design (Mrs. Y Prasanna)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Discrete Mathematics (Dr. Y Srilalitha)</t>
-        </is>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Break</t>
@@ -1212,22 +1212,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Discrete Mathematics (Sri. P Gopala Krishna)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Discrete Mathematics (Sri. P Gopala Krishna)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>Java Programming (Dr. Y J Nagendra Kumar)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Java Programming (Dr. Y J Nagendra Kumar)</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Database Management Systems (Mrs. T. Nishitha)</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Probability and Statistics (Dr. K. Prasanna Lakshmi)</t>
+          <t>Digital Logic Design (Mrs. Y Prasanna)</t>
         </is>
       </c>
     </row>
@@ -1239,17 +1239,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Discrete Mathematics (Sri. P Gopala Krishna)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>Value Ethics and Gender Culture (Mrs. N Mounika)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Database Management Systems Lab (Mrs. M Kanaka Durga Bella)</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Probability and Statistics (Dr. K. Prasanna Lakshmi)</t>
+          <t>Java Programming (Dr. Y J Nagendra Kumar)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1259,22 +1259,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Database Management Systems (Mrs. T. Nishitha)</t>
+          <t>Java Programming Lab (Mrs. A Srilakshmi)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Digital Logic Design (Mrs. Y Prasanna)</t>
+          <t>Digital Electronics Lab (Mr. P K Abhilash)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Digital Electronics Lab (Mrs.L.Hema Lalitha)</t>
+          <t>Database Management Systems Lab (Ms. I Laxmi Bindu)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Database Management Systems Lab (Mrs. M Kanaka Durga Bella)</t>
+          <t>Java Programming (Dr. Y J Nagendra Kumar)</t>
         </is>
       </c>
     </row>
@@ -1286,17 +1286,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Database Management Systems (Mrs. T. Nishitha)</t>
+          <t>Probability and Statistics (Dr. K. Prasanna Lakshmi)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Database Management Systems (Mrs. T. Nishitha)</t>
+          <t>Digital Logic Design (Mrs. Y Prasanna)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Database Management Systems Lab (Mrs. M Kanaka Durga Bella)</t>
+          <t>Database Management Systems (Dr. V N Ganapathi Raju)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1306,22 +1306,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Digital Logic Design (Mrs. Y Prasanna)</t>
+          <t>Digital Electronics Lab (Mr. P K Abhilash)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Discrete Mathematics (Dr. Y Srilalitha)</t>
+          <t>Probability and Statistics (Dr. K. Prasanna Lakshmi)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Probability and Statistics (Dr. K. Prasanna Lakshmi)</t>
+          <t>Database Management Systems (Dr. V N Ganapathi Raju)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Java Programming Lab (Mrs. A Srilakshmi)</t>
+          <t>Discrete Mathematics (Sri. P Gopala Krishna)</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Web Programming Lab (Mrs. P Prathibha Swaraj)</t>
+          <t>Introduction to Data Science (Mrs. Vemula Divya)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Web Programming (K Manasa)</t>
+          <t>Introduction to Data Science (Mrs. Vemula Divya)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Warehousing and Data Mining (Dr. V Akila)</t>
+          <t>Software Engineering (Mrs. T N P Madhuri)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Introduction to Data Science (Mrs. Vemula Divya)</t>
+          <t>Web Programming (Sri. G Vijendar Reddy)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Constitution of India (Mrs. A Vani Pushpavathi)</t>
+          <t>Software Engineering (Mrs. T N P Madhuri)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Software Engineering (Mrs. T N P Madhuri)</t>
+          <t>Artificial Intelligence Lab Using Python (Mrs. M Kanaka Durga Bella)</t>
         </is>
       </c>
     </row>
@@ -1449,42 +1449,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Data Warehousing and Data Mining (Mrs. G D Vijaya Lakshmi)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Internet of Things and Applications Lab (Mrs. A Srilakshmi)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Data Warehousing and Data Mining (Mrs. G D Vijaya Lakshmi)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Web Programming Lab (Mrs. P Prathibha Swaraj)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Break</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>Software Engineering (Mrs. T N P Madhuri)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Web Programming (K Manasa)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Web Programming (K Manasa)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence Lab Using Python (Mrs. M Kanaka Durga Bella)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Break</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Web Programming Lab (Mrs. P Prathibha Swaraj)</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Lab Using Python (Mrs. M Kanaka Durga Bella)</t>
+          <t>Web Programming (Sri. G Vijendar Reddy)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Data Warehousing and Data Mining (Dr. V Akila)</t>
+          <t>Internet of Things and Applications Lab (Mrs. A Srilakshmi)</t>
         </is>
       </c>
     </row>
@@ -1496,42 +1496,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Software Engineering (Mrs. T N P Madhuri)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Constitution of India (Mrs. A Vani Pushpavathi)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Web Programming Lab (Mrs. P Prathibha Swaraj)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Artificial Intelligence (Mr. P K Abhilash)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Break</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Software Engineering (Mrs. T N P Madhuri)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Artificial Intelligence (Mr. P K Abhilash)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Data Warehousing and Data Mining (Dr. V Akila)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Web Programming Lab (Mrs. P Prathibha Swaraj)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Break</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Software Engineering (Mrs. T N P Madhuri)</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Software Engineering (Mrs. T N P Madhuri)</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Introduction to Data Science (Mrs. Vemula Divya)</t>
+          <t>Data Warehousing and Data Mining (Mrs. G D Vijaya Lakshmi)</t>
         </is>
       </c>
     </row>
@@ -1543,22 +1543,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Software Engineering (Mrs. T N P Madhuri)</t>
+          <t>Web Programming (Sri. G Vijendar Reddy)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Web Programming Lab (Mrs. P Prathibha Swaraj)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>Constitution of India (Mrs. A Vani Pushpavathi)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Internet of Things and Applications Lab (Mrs. A Srilakshmi)</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Internet of Things and Applications Lab (Mrs. A Srilakshmi)</t>
+          <t>Data Warehousing and Data Mining (Mrs. G D Vijaya Lakshmi)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1568,17 +1568,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>Web Programming (Sri. G Vijendar Reddy)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Data Warehousing and Data Mining (Mrs. G D Vijaya Lakshmi)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Artificial Intelligence (Mr. P K Abhilash)</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Data Warehousing and Data Mining (Dr. V Akila)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Data Warehousing and Data Mining (Dr. V Akila)</t>
         </is>
       </c>
     </row>
@@ -1590,42 +1590,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Web Programming (K Manasa)</t>
+          <t>Artificial Intelligence (Mr. P K Abhilash)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Artificial Intelligence Lab Using Python (Mrs. M Kanaka Durga Bella)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Introduction to Data Science (Mrs. Vemula Divya)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Constitution of India (Mrs. A Vani Pushpavathi)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Break</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Web Programming (Sri. G Vijendar Reddy)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Lab Using Python (Mrs. M Kanaka Durga Bella)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>Artificial Intelligence (Mr. P K Abhilash)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Web Programming (K Manasa)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Introduction to Data Science (Mrs. Vemula Divya)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Break</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence (Mr. P K Abhilash)</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence Lab Using Python (Mrs. M Kanaka Durga Bella)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Constitution of India (Mrs. A Vani Pushpavathi)</t>
         </is>
       </c>
     </row>
@@ -1706,42 +1706,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (Mrs. D Preethi)</t>
+          <t>Constitution of India (Mrs. A Vani Pushpavathi)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Web Programming (Dr. G Prasanthi)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Data Warehousing and Data Mining (Dr. V Akila)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Internet of Things and Applications Lab (Mrs. M Usha Rani)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Break</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>Artificial Intelligence Lab Using Python (Mrs. M Kanaka Durga Bella)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Web Programming (Dr. G Prasanthi)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Data Warehousing and Data Mining (Mrs. G D Vijaya Lakshmi)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Break</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Internet of Things and Applications Lab (Mrs. M Usha Rani)</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Constitution of India (Mrs. A Srilakshmi)</t>
+          <t>Introduction to Data Science (Mrs. M Pavithra)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (Mrs. D Preethi)</t>
+          <t>Web Programming Lab (Mrs. T. Nishitha)</t>
         </is>
       </c>
     </row>
@@ -1753,42 +1753,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Artificial Intelligence (Mrs. D Preethi)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Software Engineering (Mrs. G D Vijaya Lakshmi)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Lab Using Python (Mrs. M Kanaka Durga Bella)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Web Programming Lab (Mrs. T. Nishitha)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Break</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>Internet of Things and Applications Lab (Mrs. M Usha Rani)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Web Programming Lab (Mrs. T. Nishitha)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Constitution of India (Mrs. A Srilakshmi)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence (Mrs. D Preethi)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Break</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Introduction to Data Science (Mrs. M Pavithra)</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Data Warehousing and Data Mining (Mrs. G D Vijaya Lakshmi)</t>
+          <t>Internet of Things and Applications Lab (Mrs. M Usha Rani)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Web Programming Lab (Mrs. T. Nishitha)</t>
+          <t>Data Warehousing and Data Mining (Dr. V Akila)</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Constitution of India (Mrs. A Srilakshmi)</t>
+          <t>Data Warehousing and Data Mining (Dr. V Akila)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Data Warehousing and Data Mining (Mrs. G D Vijaya Lakshmi)</t>
+          <t>Software Engineering (Mrs. G D Vijaya Lakshmi)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Software Engineering (Mrs.L.Hema Lalitha)</t>
+          <t>Constitution of India (Mrs. A Vani Pushpavathi)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Software Engineering (Mrs.L.Hema Lalitha)</t>
+          <t>Software Engineering (Mrs. G D Vijaya Lakshmi)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Web Programming (Dr. G Prasanthi)</t>
+          <t>Constitution of India (Mrs. A Vani Pushpavathi)</t>
         </is>
       </c>
     </row>
@@ -1847,14 +1847,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Data Warehousing and Data Mining (Dr. V Akila)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>Artificial Intelligence (Mrs. D Preethi)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Software Engineering (Mrs.L.Hema Lalitha)</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Web Programming (Dr. G Prasanthi)</t>
@@ -1862,27 +1862,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Artificial Intelligence Lab Using Python (Mrs. M Kanaka Durga Bella)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Break</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence (Mrs. D Preethi)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>Web Programming (Dr. G Prasanthi)</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Break</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence Lab Using Python (Mrs. M Kanaka Durga Bella)</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence (Mrs. D Preethi)</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Data Warehousing and Data Mining (Mrs. G D Vijaya Lakshmi)</t>
+          <t>Data Warehousing and Data Mining (Dr. V Akila)</t>
         </is>
       </c>
     </row>
@@ -1894,24 +1894,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Artificial Intelligence (Mrs. D Preethi)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Web Programming Lab (Mrs. T. Nishitha)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Software Engineering (Mrs. G D Vijaya Lakshmi)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Web Programming (Dr. G Prasanthi)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Data Warehousing and Data Mining (Mrs. G D Vijaya Lakshmi)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Internet of Things and Applications Lab (Mrs. M Usha Rani)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence Lab Using Python (Mrs. M Kanaka Durga Bella)</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>Break</t>
@@ -1919,17 +1919,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Software Engineering (Mrs.L.Hema Lalitha)</t>
+          <t>Software Engineering (Mrs. G D Vijaya Lakshmi)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Web Programming Lab (Mrs. T. Nishitha)</t>
+          <t>Artificial Intelligence (Mrs. D Preethi)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Software Engineering (Mrs.L.Hema Lalitha)</t>
+          <t>Web Programming (Dr. G Prasanthi)</t>
         </is>
       </c>
     </row>
@@ -2010,42 +2010,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Artificial Intelligence (Mrs. D Preethi)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence (Mrs. D Preethi)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Introduction to Data Science (Mrs. M Pavithra)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Data Warehousing and Data Mining (Mrs. G D Vijaya Lakshmi)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Break</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Introduction to Data Science (Mrs. M Pavithra)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Web Programming Lab (Mrs. T. Nishitha)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>Internet of Things and Applications Lab (Mrs. R Madhuri)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Data Warehousing and Data Mining (Mrs. G D Vijaya Lakshmi)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Introduction to Data Science (Mrs. D Preethi)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Software Engineering (Mrs. Vemula Divya)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Break</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Introduction to Data Science (Mrs. D Preethi)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence Lab Using Python (Mrs. P Prathibha Swaraj)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Data Warehousing and Data Mining (Mrs. G D Vijaya Lakshmi)</t>
         </is>
       </c>
     </row>
@@ -2057,42 +2057,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Introduction to Data Science (Mrs. D Preethi)</t>
+          <t>Software Engineering (Mrs. Vemula Divya)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Web Programming (K Manasa)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Web Programming (K Manasa)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Internet of Things and Applications Lab (Mrs. R Madhuri)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Break</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Lab Using Python (Mrs. P Prathibha Swaraj)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>Data Warehousing and Data Mining (Mrs. G D Vijaya Lakshmi)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence Lab Using Python (Mrs. P Prathibha Swaraj)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Web Programming (Sri. G Vijendar Reddy)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Break</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Web Programming Lab (Mrs. T. Nishitha)</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Web Programming (Sri. G Vijendar Reddy)</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Lab Using Python (Mrs. P Prathibha Swaraj)</t>
+          <t>Software Engineering (Mrs. Vemula Divya)</t>
         </is>
       </c>
     </row>
@@ -2104,42 +2104,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Data Warehousing and Data Mining (Mrs. G D Vijaya Lakshmi)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Internet of Things and Applications Lab (Mrs. R Madhuri)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Web Programming (K Manasa)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Introduction to Data Science (Mrs. M Pavithra)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Break</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Constitution of India (Mrs. A Srilakshmi)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Lab Using Python (Mrs. P Prathibha Swaraj)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>Software Engineering (Mrs. Vemula Divya)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Web Programming (Sri. G Vijendar Reddy)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Internet of Things and Applications Lab (Mrs. R Madhuri)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Internet of Things and Applications Lab (Mrs. R Madhuri)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Break</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Software Engineering (Mrs. Vemula Divya)</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence (Mr. P K Abhilash)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Constitution of India (Mrs. A Srilakshmi)</t>
         </is>
       </c>
     </row>
@@ -2151,22 +2151,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Web Programming (Sri. G Vijendar Reddy)</t>
+          <t>Data Warehousing and Data Mining (Mrs. G D Vijaya Lakshmi)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Data Warehousing and Data Mining (Mrs. G D Vijaya Lakshmi)</t>
+          <t>Web Programming Lab (Mrs. T. Nishitha)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (Mr. P K Abhilash)</t>
+          <t>Artificial Intelligence (Mrs. D Preethi)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Warehousing and Data Mining (Mrs. G D Vijaya Lakshmi)</t>
+          <t>Artificial Intelligence Lab Using Python (Mrs. P Prathibha Swaraj)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (Mr. P K Abhilash)</t>
+          <t>Constitution of India (Mrs. A Srilakshmi)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Constitution of India (Mrs. A Srilakshmi)</t>
+          <t>Web Programming (K Manasa)</t>
         </is>
       </c>
     </row>
@@ -2198,42 +2198,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Web Programming (Sri. G Vijendar Reddy)</t>
+          <t>Web Programming Lab (Mrs. T. Nishitha)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Data Warehousing and Data Mining (Mrs. G D Vijaya Lakshmi)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence (Mrs. D Preethi)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Software Engineering (Mrs. Vemula Divya)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Break</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Web Programming (K Manasa)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>Constitution of India (Mrs. A Srilakshmi)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Software Engineering (Mrs. Vemula Divya)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Web Programming Lab (Mrs. T. Nishitha)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Break</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Web Programming Lab (Mrs. T. Nishitha)</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence (Mr. P K Abhilash)</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (Mr. P K Abhilash)</t>
+          <t>Artificial Intelligence (Mrs. D Preethi)</t>
         </is>
       </c>
     </row>
